--- a/DataTables/DetailText/剧情/005_01世子脾虚湿盛.xlsx
+++ b/DataTables/DetailText/剧情/005_01世子脾虚湿盛.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2393735-3224-4E2A-AA6D-A50B223EF39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65284BF3-37CF-479C-AA6E-182AC694B6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -543,10 +532,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>before</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>dim</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -560,10 +545,6 @@
   </si>
   <si>
     <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <t>res://Assets/Portrait/StoryNpc/shi_zi/shi_zi_before.png</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>脾虚湿盛</t>
@@ -779,6 +760,14 @@
   </si>
   <si>
     <t>世子脾虚湿盛</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Portrait/StoryNpc/shi_zi/shi_zi_sick.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>sick</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -790,7 +779,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -804,7 +793,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -825,7 +814,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -979,7 +968,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1258,24 +1247,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.73046875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="54.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="54.1328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1298,28 +1287,28 @@
         <v>17</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J1" s="17" t="s">
         <v>18</v>
       </c>
       <c r="K1" s="17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M1" s="19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N1" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O1" s="20" t="s">
         <v>19</v>
@@ -1333,7 +1322,7 @@
         <v>40</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>22</v>
@@ -1348,18 +1337,18 @@
       <c r="G2" s="1"/>
       <c r="H2" s="5"/>
       <c r="I2" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>39</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="O2" s="1" t="b">
         <v>1</v>
@@ -1437,14 +1426,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1486,7 +1475,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>24</v>
@@ -1507,7 +1496,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
@@ -1529,10 +1518,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>27</v>
@@ -1553,7 +1542,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
@@ -1575,7 +1564,7 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
@@ -1597,7 +1586,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="1" t="s">
@@ -1619,7 +1608,7 @@
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
@@ -1641,7 +1630,7 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
@@ -1679,10 +1668,10 @@
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>36</v>
@@ -1703,7 +1692,7 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
@@ -1725,10 +1714,10 @@
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>46</v>
@@ -1749,7 +1738,7 @@
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
@@ -1770,10 +1759,10 @@
         <v>10</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H15" s="14" t="s">
         <v>45</v>
@@ -1794,7 +1783,7 @@
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="14" t="s">

--- a/DataTables/DetailText/剧情/005_01世子脾虚湿盛.xlsx
+++ b/DataTables/DetailText/剧情/005_01世子脾虚湿盛.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65284BF3-37CF-479C-AA6E-182AC694B6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA3D1AC-E7DD-47A9-8B89-92C198C6896E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -779,7 +790,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -793,7 +804,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -814,7 +825,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -968,7 +979,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1247,24 +1258,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.73046875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="54.1328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="54.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1426,14 +1437,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1648,7 +1659,9 @@
       <c r="D10" s="2"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="G10" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="H10" s="3" t="s">
         <v>35</v>
       </c>
@@ -1670,9 +1683,7 @@
       <c r="F11" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>61</v>
-      </c>
+      <c r="G11" s="2"/>
       <c r="H11" s="3" t="s">
         <v>36</v>
       </c>

--- a/DataTables/DetailText/剧情/005_01世子脾虚湿盛.xlsx
+++ b/DataTables/DetailText/剧情/005_01世子脾虚湿盛.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA3D1AC-E7DD-47A9-8B89-92C198C6896E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D4DE6D6-5474-4FF3-870A-CA37043A079E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -425,10 +425,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>楚恭王</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <r>
       <t>草民拜见王</t>
     </r>
@@ -779,6 +775,10 @@
   </si>
   <si>
     <t>sick</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>楚王</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1298,28 +1298,28 @@
         <v>17</v>
       </c>
       <c r="G1" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="16" t="s">
         <v>56</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>57</v>
       </c>
       <c r="J1" s="17" t="s">
         <v>18</v>
       </c>
       <c r="K1" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L1" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="M1" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="M1" s="19" t="s">
-        <v>55</v>
-      </c>
       <c r="N1" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O1" s="20" t="s">
         <v>19</v>
@@ -1333,7 +1333,7 @@
         <v>40</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>22</v>
@@ -1348,18 +1348,18 @@
       <c r="G2" s="1"/>
       <c r="H2" s="5"/>
       <c r="I2" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>39</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O2" s="1" t="b">
         <v>1</v>
@@ -1486,7 +1486,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>24</v>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
@@ -1529,10 +1529,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>27</v>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="1" t="s">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
@@ -1660,7 +1660,7 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>35</v>
@@ -1674,14 +1674,14 @@
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="3" t="s">
@@ -1703,11 +1703,11 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1718,20 +1718,20 @@
         <v>7</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1742,14 +1742,14 @@
         <v>7</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
@@ -1764,19 +1764,19 @@
         <v>7</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1787,18 +1787,18 @@
         <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:8">

--- a/DataTables/DetailText/剧情/005_01世子脾虚湿盛.xlsx
+++ b/DataTables/DetailText/剧情/005_01世子脾虚湿盛.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D4DE6D6-5474-4FF3-870A-CA37043A079E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E25E64-2AB8-4A83-B033-76576B2981DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -152,32 +152,6 @@
   </si>
   <si>
     <r>
-      <t>奉楚恭王敕令，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>请</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>先生去王府走一趟。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
       <t>是什么人病了要我去看病</t>
     </r>
     <r>
@@ -779,6 +753,32 @@
   </si>
   <si>
     <t>楚王</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>奉楚王敕令，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>请</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>先生去王府走一趟。</t>
+    </r>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1298,28 +1298,28 @@
         <v>17</v>
       </c>
       <c r="G1" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="16" t="s">
         <v>55</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>56</v>
       </c>
       <c r="J1" s="17" t="s">
         <v>18</v>
       </c>
       <c r="K1" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L1" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="M1" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="M1" s="19" t="s">
-        <v>54</v>
-      </c>
       <c r="N1" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O1" s="20" t="s">
         <v>19</v>
@@ -1330,16 +1330,16 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>23</v>
@@ -1348,18 +1348,18 @@
       <c r="G2" s="1"/>
       <c r="H2" s="5"/>
       <c r="I2" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O2" s="1" t="b">
         <v>1</v>
@@ -1486,7 +1486,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>24</v>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
@@ -1529,10 +1529,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>27</v>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
@@ -1597,11 +1597,11 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="1" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1619,11 +1619,11 @@
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1641,11 +1641,11 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1660,10 +1660,10 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1674,18 +1674,18 @@
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1696,18 +1696,18 @@
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1718,20 +1718,20 @@
         <v>7</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1742,18 +1742,18 @@
         <v>7</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1764,19 +1764,19 @@
         <v>7</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1787,18 +1787,18 @@
         <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:8">

--- a/DataTables/DetailText/剧情/005_01世子脾虚湿盛.xlsx
+++ b/DataTables/DetailText/剧情/005_01世子脾虚湿盛.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E25E64-2AB8-4A83-B033-76576B2981DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5396C361-2E96-408D-BBE9-D16A610D213E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5317" yWindow="3863" windowWidth="21601" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -224,52 +213,6 @@
   </si>
   <si>
     <r>
-      <t>一夜舟车</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>劳顿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，李</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>东</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>璧到了楚恭王府。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
       <t>您就是李神医啊，比我想得要年</t>
     </r>
     <r>
@@ -778,6 +721,52 @@
         <charset val="128"/>
       </rPr>
       <t>先生去王府走一趟。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>一夜舟车</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>劳顿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，李</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>东</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>璧到了楚王府。</t>
     </r>
     <phoneticPr fontId="2"/>
   </si>
@@ -790,7 +779,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -804,7 +793,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -825,7 +814,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -979,7 +968,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1258,24 +1247,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.73046875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="54.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="54.1328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1298,28 +1287,28 @@
         <v>17</v>
       </c>
       <c r="G1" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" s="16" t="s">
         <v>54</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>55</v>
       </c>
       <c r="J1" s="17" t="s">
         <v>18</v>
       </c>
       <c r="K1" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L1" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M1" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="M1" s="19" t="s">
-        <v>53</v>
-      </c>
       <c r="N1" s="19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O1" s="20" t="s">
         <v>19</v>
@@ -1330,16 +1319,16 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>23</v>
@@ -1348,18 +1337,18 @@
       <c r="G2" s="1"/>
       <c r="H2" s="5"/>
       <c r="I2" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O2" s="1" t="b">
         <v>1</v>
@@ -1437,14 +1426,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1486,7 +1475,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>24</v>
@@ -1507,7 +1496,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
@@ -1529,10 +1518,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>27</v>
@@ -1553,7 +1542,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
@@ -1575,7 +1564,7 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
@@ -1597,11 +1586,11 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1619,7 +1608,7 @@
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
@@ -1641,7 +1630,7 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
@@ -1660,10 +1649,10 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1674,18 +1663,18 @@
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1696,18 +1685,18 @@
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1718,20 +1707,20 @@
         <v>7</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1742,18 +1731,18 @@
         <v>7</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1764,19 +1753,19 @@
         <v>7</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1787,18 +1776,18 @@
         <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:8">

--- a/DataTables/DetailText/剧情/005_01世子脾虚湿盛.xlsx
+++ b/DataTables/DetailText/剧情/005_01世子脾虚湿盛.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5396C361-2E96-408D-BBE9-D16A610D213E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F491395-D9DF-42E5-B4A5-2C4CA2BFBE9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5317" yWindow="3863" windowWidth="21601" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -101,10 +112,6 @@
     <t>SortIndex</t>
   </si>
   <si>
-    <t>scene_enter</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>night</t>
   </si>
   <si>
@@ -137,32 +144,6 @@
   </si>
   <si>
     <t>王府护卫</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>是什么人病了要我去看病</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>吗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>？</t>
-    </r>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -376,82 +357,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <r>
-      <t>犬子前几天突然病了，卧床不起。精神萎靡，食欲不振。小王</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>请</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>了好几位大夫，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>给</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>开了好多方子，都不见好</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>转</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>。眼见着人一天比一天瘦，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>在这么下去怕是要坏事了…</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>先生，小王就这么一个儿子，请您救救孩子吧。</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -700,7 +605,7 @@
   </si>
   <si>
     <r>
-      <t>奉楚王敕令，</t>
+      <t>一夜舟车</t>
     </r>
     <r>
       <rPr>
@@ -710,6 +615,72 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
+      <t>劳顿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，李</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>东</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>璧到了楚王府。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>奉楚王</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>谕令</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
       <t>请</t>
     </r>
     <r>
@@ -726,7 +697,7 @@
   </si>
   <si>
     <r>
-      <t>一夜舟车</t>
+      <t>是什么人病了？要我去看病</t>
     </r>
     <r>
       <rPr>
@@ -736,17 +707,23 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>劳顿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，李</t>
+      <t>吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>？</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>犬子前几天突然病了，卧床不起。精神萎靡，食欲不振。小王</t>
     </r>
     <r>
       <rPr>
@@ -756,19 +733,73 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>东</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>璧到了楚王府。</t>
-    </r>
-    <phoneticPr fontId="2"/>
+      <t>请</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>了好几位大夫，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>开了好多方子，都不见好</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>转</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。眼见着人一天比一天瘦，再</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这么下去怕是要坏事了…</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>night_end</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -779,7 +810,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -793,7 +824,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -814,7 +845,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -968,7 +999,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1247,24 +1278,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.73046875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="54.1328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="54.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1287,28 +1318,28 @@
         <v>17</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J1" s="17" t="s">
         <v>18</v>
       </c>
       <c r="K1" s="17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M1" s="19" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="N1" s="19" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O1" s="20" t="s">
         <v>19</v>
@@ -1319,36 +1350,36 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="5"/>
       <c r="I2" s="13" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="O2" s="1" t="b">
         <v>1</v>
@@ -1426,14 +1457,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1475,10 +1506,10 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1489,18 +1520,18 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1511,20 +1542,20 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1535,18 +1566,18 @@
         <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1557,18 +1588,18 @@
         <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1579,18 +1610,18 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1601,18 +1632,18 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1623,18 +1654,18 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1649,10 +1680,10 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1663,18 +1694,18 @@
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1685,18 +1716,18 @@
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1707,20 +1738,20 @@
         <v>7</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1731,18 +1762,18 @@
         <v>7</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1753,19 +1784,19 @@
         <v>7</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1776,18 +1807,18 @@
         <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="14" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:8">

--- a/DataTables/DetailText/剧情/005_01世子脾虚湿盛.xlsx
+++ b/DataTables/DetailText/剧情/005_01世子脾虚湿盛.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F491395-D9DF-42E5-B4A5-2C4CA2BFBE9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEB2E84-9ABD-47BD-A9DD-59BF7E5F9052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="63">
   <si>
     <t>StoryID</t>
   </si>
@@ -358,18 +347,6 @@
   </si>
   <si>
     <t>先生，小王就这么一个儿子，请您救救孩子吧。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>dim</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>normal</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>hide</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -810,7 +787,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -824,7 +801,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -845,7 +822,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -999,7 +976,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1278,24 +1255,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.73046875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="54.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="54.1328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1318,28 +1295,28 @@
         <v>17</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J1" s="17" t="s">
         <v>18</v>
       </c>
       <c r="K1" s="17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="M1" s="19" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N1" s="19" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="O1" s="20" t="s">
         <v>19</v>
@@ -1353,10 +1330,10 @@
         <v>36</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>34</v>
@@ -1368,18 +1345,18 @@
       <c r="G2" s="1"/>
       <c r="H2" s="5"/>
       <c r="I2" s="13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>35</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O2" s="1" t="b">
         <v>1</v>
@@ -1457,14 +1434,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1506,7 +1483,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>23</v>
@@ -1526,9 +1503,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="8" t="s">
-        <v>42</v>
-      </c>
+      <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
         <v>25</v>
@@ -1548,11 +1523,9 @@
         <v>10</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="8" t="s">
-        <v>44</v>
-      </c>
+      <c r="F4" s="8"/>
       <c r="G4" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>26</v>
@@ -1572,9 +1545,7 @@
         <v>9</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="8" t="s">
-        <v>42</v>
-      </c>
+      <c r="F5" s="8"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
         <v>28</v>
@@ -1594,9 +1565,7 @@
         <v>9</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="8" t="s">
-        <v>42</v>
-      </c>
+      <c r="F6" s="8"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
         <v>29</v>
@@ -1616,12 +1585,10 @@
         <v>12</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="8" t="s">
-        <v>42</v>
-      </c>
+      <c r="F7" s="8"/>
       <c r="G7" s="2"/>
       <c r="H7" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1638,12 +1605,10 @@
         <v>9</v>
       </c>
       <c r="E8" s="3"/>
-      <c r="F8" s="8" t="s">
-        <v>44</v>
-      </c>
+      <c r="F8" s="8"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1660,9 +1625,7 @@
         <v>12</v>
       </c>
       <c r="E9" s="3"/>
-      <c r="F9" s="8" t="s">
-        <v>42</v>
-      </c>
+      <c r="F9" s="8"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
         <v>31</v>
@@ -1680,10 +1643,10 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1694,15 +1657,13 @@
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E11" s="3"/>
-      <c r="F11" s="8" t="s">
-        <v>42</v>
-      </c>
+      <c r="F11" s="8"/>
       <c r="G11" s="2"/>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -1722,9 +1683,7 @@
         <v>9</v>
       </c>
       <c r="E12" s="3"/>
-      <c r="F12" s="8" t="s">
-        <v>42</v>
-      </c>
+      <c r="F12" s="8"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
         <v>38</v>
@@ -1738,20 +1697,18 @@
         <v>7</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E13" s="3"/>
-      <c r="F13" s="8" t="s">
-        <v>42</v>
-      </c>
+      <c r="F13" s="8"/>
       <c r="G13" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1762,15 +1719,13 @@
         <v>7</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="3"/>
-      <c r="F14" s="8" t="s">
-        <v>42</v>
-      </c>
+      <c r="F14" s="8"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
         <v>33</v>
@@ -1790,11 +1745,9 @@
         <v>10</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>43</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="F15" s="8"/>
       <c r="H15" s="14" t="s">
         <v>40</v>
       </c>
@@ -1807,15 +1760,13 @@
         <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="3"/>
-      <c r="F16" s="8" t="s">
-        <v>44</v>
-      </c>
+      <c r="F16" s="8"/>
       <c r="G16" s="3"/>
       <c r="H16" s="14" t="s">
         <v>41</v>

--- a/DataTables/DetailText/剧情/005_01世子脾虚湿盛.xlsx
+++ b/DataTables/DetailText/剧情/005_01世子脾虚湿盛.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEB2E84-9ABD-47BD-A9DD-59BF7E5F9052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4344DB-0570-4554-B577-5B4DAD72598B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -699,84 +710,84 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <r>
-      <t>犬子前几天突然病了，卧床不起。精神萎靡，食欲不振。小王</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>请</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>了好几位大夫，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>给</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>开了好多方子，都不见好</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>转</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>。眼见着人一天比一天瘦，再</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这么下去怕是要坏事了…</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>night_end</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>犬子前些日子突然病倒了，卧床不起。精神萎靡，食欲不振。小王</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>请</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>了好几位大夫，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>开了好多方子，都不见好</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>转</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。眼见着人一天比一天瘦，再</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这么下去怕是要坏事了…</t>
+    </r>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -787,7 +798,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -801,7 +812,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -822,7 +833,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -976,7 +987,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1255,24 +1266,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.73046875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="54.1328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="54.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1333,7 +1344,7 @@
         <v>54</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>34</v>
@@ -1434,14 +1445,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1499,8 +1510,8 @@
       <c r="C3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
+      <c r="D3" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8"/>
@@ -1519,8 +1530,8 @@
       <c r="C4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
+      <c r="D4" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
@@ -1541,8 +1552,8 @@
       <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>9</v>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8"/>
@@ -1561,8 +1572,8 @@
       <c r="C6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>9</v>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="8"/>
@@ -1601,8 +1612,8 @@
       <c r="C8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>9</v>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="8"/>
@@ -1708,7 +1719,7 @@
         <v>53</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:8">

--- a/DataTables/DetailText/剧情/005_01世子脾虚湿盛.xlsx
+++ b/DataTables/DetailText/剧情/005_01世子脾虚湿盛.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4344DB-0570-4554-B577-5B4DAD72598B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E15ECD-1BE3-4B81-A8E7-456655FC79B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6202" yWindow="4012" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,26 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="63">
-  <si>
-    <t>StoryID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="66">
   <si>
     <t>LineIndex</t>
   </si>
@@ -87,28 +73,9 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
     <t>SortIndex</t>
   </si>
   <si>
@@ -282,10 +249,6 @@
       </rPr>
       <t>请先生来给犬子医治。</t>
     </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>night</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -361,37 +324,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
     <t>脾虚湿盛</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>res://Assets/Background/00</t>
     </r>
@@ -710,95 +646,179 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <r>
+      <t>犬子前些日子突然病倒了，卧床不起。精神萎靡，食欲不振。小王</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>请</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>了好几位大夫，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>开了好多方子，都不见好</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>转</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。眼见着人一天比一天瘦，再</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这么下去怕是要坏事了…</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
     <t>night_end</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>犬子前些日子突然病倒了，卧床不起。精神萎靡，食欲不振。小王</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>请</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>了好几位大夫，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>给</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>开了好多方子，都不见好</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>转</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>。眼见着人一天比一天瘦，再</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这么下去怕是要坏事了…</t>
-    </r>
-    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -812,7 +832,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -833,7 +853,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -862,13 +882,27 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Noto Sans JP"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -883,20 +917,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -927,7 +963,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -953,9 +989,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -974,20 +1007,43 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1265,177 +1321,205 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="54.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="51.1328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:20" s="23" customFormat="1">
+      <c r="A1" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="K1" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="L1" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M1" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="N1" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="O1" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="P1" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q1" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="R1" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="S1" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:20" s="23" customFormat="1">
+      <c r="A2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="24"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="L1" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="O1" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="P1" s="20" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="M2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="O2" s="1" t="b">
+      <c r="O2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="C3" s="10"/>
-      <c r="H3" s="18"/>
-      <c r="O3" s="11"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="C4" s="10"/>
-      <c r="H4" s="18"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="C5" s="10"/>
-      <c r="H5" s="18"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="H6" s="18"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="H7" s="18"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="H8" s="18"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="H9" s="18"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="H10" s="18"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="H11" s="18"/>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="H12" s="18"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="H13" s="18"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="H14" s="18"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="H15" s="18"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="H16" s="18"/>
+      <c r="T2" s="26"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="9"/>
+      <c r="H3" s="15"/>
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="C4" s="9"/>
+      <c r="H4" s="15"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="C5" s="9"/>
+      <c r="H5" s="15"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="H6" s="15"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="H7" s="15"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="H8" s="15"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="H9" s="15"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="H10" s="15"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="H11" s="15"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="H12" s="15"/>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="H13" s="15"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="H14" s="15"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="H15" s="15"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="H16" s="15"/>
     </row>
     <row r="17" spans="8:8">
-      <c r="H17" s="18"/>
+      <c r="H17" s="15"/>
     </row>
     <row r="18" spans="8:8">
-      <c r="H18" s="18"/>
+      <c r="H18" s="15"/>
     </row>
     <row r="19" spans="8:8">
-      <c r="H19" s="18"/>
+      <c r="H19" s="15"/>
     </row>
     <row r="20" spans="8:8">
-      <c r="H20" s="18"/>
+      <c r="H20" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C2" xr:uid="{4533F412-03C7-4AC2-A8B6-F7A9829EFC7E}">
+      <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{391506E9-2FA3-4996-951D-5A632FFA3DC1}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{3FCD05F8-3708-4B1A-B038-67E9DBAEDCCB}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2" xr:uid="{BCC60B1E-A8B0-443A-B0D7-90361A25109A}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K2" xr:uid="{2006E4FB-1C23-4F2D-84D1-9CD103161FA9}">
+      <formula1>"cured,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1445,41 +1529,41 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1487,17 +1571,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>23</v>
+        <v>35</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1505,19 +1589,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1525,21 +1609,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1547,19 +1631,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1567,19 +1651,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="8"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1587,19 +1671,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="8"/>
       <c r="G7" s="2"/>
       <c r="H7" s="1" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1607,19 +1691,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="8"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1627,19 +1711,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="8"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1647,17 +1731,17 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="2" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1665,19 +1749,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="8"/>
       <c r="G11" s="2"/>
       <c r="H11" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1685,19 +1769,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="8"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1705,21 +1789,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="8"/>
       <c r="G13" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1727,19 +1811,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="8"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1747,20 +1831,20 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>39</v>
+        <v>6</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>31</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>56</v>
+        <v>9</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="F15" s="8"/>
-      <c r="H15" s="14" t="s">
-        <v>40</v>
+      <c r="H15" s="13" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1768,30 +1852,30 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="8"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="14" t="s">
-        <v>41</v>
+      <c r="H16" s="13" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="3"/>
       <c r="B17" s="1"/>
-      <c r="C17" s="13"/>
+      <c r="C17" s="12"/>
       <c r="D17" s="2"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="15"/>
+      <c r="H17" s="14"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="3"/>

--- a/DataTables/DetailText/剧情/005_01世子脾虚湿盛.xlsx
+++ b/DataTables/DetailText/剧情/005_01世子脾虚湿盛.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E15ECD-1BE3-4B81-A8E7-456655FC79B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467AA4B0-57DB-48FF-A61C-F852FF53CD97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6202" yWindow="4012" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19740" yWindow="5400" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="67">
   <si>
     <t>LineIndex</t>
   </si>
@@ -808,6 +819,10 @@
   </si>
   <si>
     <t>night_end</t>
+  </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="10"/>
   </si>
 </sst>
 </file>
@@ -818,7 +833,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -832,7 +847,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -853,7 +868,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -963,7 +978,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1041,9 +1056,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1322,26 +1340,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="51.1328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="51.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="23" customFormat="1">
+    <row r="1" spans="1:20" s="23" customFormat="1" ht="18">
       <c r="A1" s="16" t="s">
         <v>47</v>
       </c>
@@ -1403,7 +1421,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="23" customFormat="1">
+    <row r="2" spans="1:20" s="23" customFormat="1" ht="18">
       <c r="A2" s="5" t="s">
         <v>28</v>
       </c>
@@ -1526,21 +1544,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1565,8 +1583,11 @@
       <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1583,8 +1604,9 @@
       <c r="H2" s="11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1603,8 +1625,9 @@
       <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1625,8 +1648,9 @@
       <c r="H4" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1645,8 +1669,9 @@
       <c r="H5" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1665,8 +1690,9 @@
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1685,8 +1711,9 @@
       <c r="H7" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1705,8 +1732,9 @@
       <c r="H8" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1725,8 +1753,9 @@
       <c r="H9" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1743,8 +1772,9 @@
       <c r="H10" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1763,8 +1793,9 @@
       <c r="H11" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1783,8 +1814,9 @@
       <c r="H12" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1805,8 +1837,9 @@
       <c r="H13" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1825,8 +1858,9 @@
       <c r="H14" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1846,8 +1880,9 @@
       <c r="H15" s="13" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1866,8 +1901,9 @@
       <c r="H16" s="13" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="3"/>
       <c r="B17" s="1"/>
       <c r="C17" s="12"/>
@@ -1876,8 +1912,9 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="14"/>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1886,8 +1923,9 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -1896,8 +1934,9 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1906,8 +1945,9 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1916,8 +1956,9 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -1926,8 +1967,9 @@
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1936,8 +1978,9 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -1946,6 +1989,7 @@
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
